--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260612.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260612.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>18.10%</t>
+          <t>18.16%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>68,000,000</t>
+          <t>72,400,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>5.35%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>4.69%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>4.47%</t>
         </is>
       </c>
     </row>
@@ -704,95 +704,95 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>4.33%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>1,350,000</t>
+          <t>12,101,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.90%</t>
+          <t>3.95%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>12,101,000</t>
+          <t>38,000,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.73%</t>
+          <t>3.62%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>4,700,000</t>
+          <t>1,350,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.61%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>36,000,000</t>
+          <t>4,700,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.43%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>870,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -836,46 +836,46 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,100,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>1,170,000</t>
+          <t>2,100,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -902,51 +902,51 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>830,000</t>
+          <t>5,900,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>5,600,000</t>
+          <t>830,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1078,112 +1078,112 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>430,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>9,911,000</t>
+          <t>430,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>830,000</t>
+          <t>9,911,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,334,000</t>
+          <t>830,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>690,000</t>
+          <t>1,334,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,66 +1195,66 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>165,000</t>
+          <t>1,497,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>5,600,000</t>
+          <t>570,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,497,000</t>
+          <t>5,600,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1452,51 +1452,51 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>957,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>957,000</t>
+          <t>870,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>870,000</t>
+          <t>916,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,100 +1591,100 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,010,000</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>340,000</t>
+          <t>1,010,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>5,859,418,494</t>
+          <t>7,442,604,797</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-1,955,569,139</t>
+          <t>-2,292,205,803</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
